--- a/materials/05_행정처리_도움받기/추가_2025 오현초 체험학습 전세버스 견적서(25.10.23).xlsx
+++ b/materials/05_행정처리_도움받기/추가_2025 오현초 체험학습 전세버스 견적서(25.10.23).xlsx
@@ -128,7 +128,7 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>홍길동</t>
+    <t>류건우</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
